--- a/Paket_10_Matematika_TKA_SD.xlsx
+++ b/Paket_10_Matematika_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 10 Matematika" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 1: contoh soal numerasi sederhana.</t>
+          <t>Sebuah peternakan ayam menghasilkan 450 butir telur setiap hari. Telur-telur tersebut dikemas ke dalam baki telur yang masing-masing memuat 30 butir. Jika setiap baki dijual dengan harga Rp55.000, berapakah total pendapatan peternakan dari penjualan telur selama 5 hari?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. Rp3.850.000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Rp4.125.000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. Rp4.400.000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Rp4.675.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 2: contoh soal numerasi sederhana.</t>
+          <t>Seekor lumba-lumba mula-mula berada 15 meter di bawah permukaan laut. Lumba-lumba tersebut melompat ke atas setinggi 18 meter melewati permukaan air, lalu menyelam kembali sedalam 7 meter dari titik tertinggi lompatannya. Di kedalaman berapa meter posisi lumba-lumba sekarang relatif terhadap permukaan air?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. -4 meter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 4 meter</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. -7 meter</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 7 meter</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 3: contoh soal numerasi sederhana.</t>
+          <t>Dalam survei minat baca 160 siswa SD Merdeka: • 35% siswa gemar membaca buku cerita rakyat • 1/4 bagian gemar membaca ensiklopedia ilmiah • Sisanya gemar membaca komik edukasi Berapa banyak siswa yang gemar membaca komik edukasi?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 56 anak</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 64 anak</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 72 anak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 80 anak</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,7 +592,11 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,27 +606,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 4: contoh soal numerasi sederhana.</t>
+          <t>Tiga kelompok ronda malam berpatroli dengan jeda waktu berbeda: Kelompok A setiap 30 menit, Kelompok B setiap 45 menit, dan Kelompok C setiap 60 menit. Jika mereka mulai berpatroli bersama pada pukul 21.00 WIB, pada pukul berapakah mereka akan berpatroli bersamaan kembali?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 23.30 WIB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 00.00 WIB</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 00.30 WIB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 01.00 WIB</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,17 +637,21 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 5: contoh soal numerasi sederhana.</t>
+          <t>Panitia bakti sosial mengumpulkan 105 botol minyak goreng, 140 bungkus gula pasir, dan 175 mie instan. Paket-paket tersebut akan disalurkan kepada warga terdampak banjir dengan isi setiap paket persis sama tanpa sisa. Manakah pernyataan yang BENAR? (Jawaban benar lebih dari satu) ☐ A. Jumlah paket sembako terbanyak yang dapat dibuat adalah 35 paket ☐ B. Setiap paket sembako berisi 3 botol minyak goreng ☐ C. Setiap paket sembako berisi 4 bungkus gula pasir dan 5 mie instan ☐ D. Total seluruh isi sembako dalam satu paket adalah 14 barang [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -666,7 +682,11 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -676,27 +696,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 6: contoh soal numerasi sederhana.</t>
+          <t>Pada sebuah peta pariwisata provinsi, jarak antara Candi Borobudur dan Keraton Yogyakarta digambar 8,4 cm. Jika skala peta adalah 1 : 500.000, berapakah jarak sebenarnya antara kedua lokasi wisata tersebut?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 36 km</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 40 km</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 42 km</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 45 km</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -707,17 +727,21 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 7: contoh soal numerasi sederhana.</t>
+          <t>Dalam rangka festival kuliner, Restoran Nusantara menawarkan paket makan hemat: • Paket Hemat 1: Nasi Liwet Komplit Rp45.000 (Diskon 20%) • Paket Hemat 2: Ayam Bakar Madu Rp60.000 (Diskon 25%) • Paket Minum: Es Kelapa Muda Gula Jawa Rp16.000 (Diskon 50%) Tentukan kebenaran dari pernyataan-pernyataan berikut! [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -748,7 +772,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +786,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 8: contoh soal numerasi sederhana.</t>
+          <t>Sebuah festival pentas seni menampilkan tiga mata acara utama: pertunjukan tari tradisional selama 1 jam 45 menit 30 detik, drama musikal anak selama 2 jam 18 menit 45 detik, dan parade band sekolah selama 55 menit 15 detik. Berapakah total durasi festival seni tersebut?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 4 jam 59 menit 30 detik</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 5 jam 00 menit 30 detik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 5 jam 19 menit 30 detik</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 5 jam 29 menit 30 detik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +817,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +831,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 9: contoh soal numerasi sederhana.</t>
+          <t>Bus Trans Antar Kota melaju dari terminal Surabaya menuju terminal Solo dengan kecepatan rata-rata 75 km/jam menempuh jarak 225 km. Jika bus sempat terjebak antrean di gerbang tol selama 20 menit dan tiba di terminal Solo tepat pukul 12.00 WIB, pada pukul berapakah bus tersebut berangkat dari Surabaya?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 08.20 WIB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 08.40 WIB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 09.00 WIB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 09.20 WIB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +862,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +876,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 10: contoh soal numerasi sederhana.</t>
+          <t>Seorang pedagang pakaian membeli 3 gros kancing baju, 4 kodi kaos polos, dan 5 lusin celana pendek. Berapa jumlah total seluruh potong barang yang dibeli oleh pedagang tersebut?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 562 buah</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 572 buah</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 582 buah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 592 buah</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,7 +907,11 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -881,27 +921,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 11: contoh soal numerasi sederhana.</t>
+          <t>Sebuah mobil tangki pemadam kebakaran membawa 6.000 liter air. Selang pemadam menyemprotkan air dengan debit konstan 250 liter per menit. Berapa menit waktu yang dibutuhkan hingga seluruh air di dalam tangki habis disemprotkan?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 20 menit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 24 menit</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 28 menit</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 32 menit</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,17 +952,21 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 12: contoh soal numerasi sederhana.</t>
+          <t>Perhatikan bangun datar layang-layang PQRS berikut dengan panjang diagonal PR = 24 cm dan QS = 16 cm yang berpotongan tegak lurus di titik O. Manakah pernyataan berikut yang BENAR? (Jawaban benar lebih dari satu) ☐ A. Luas layang-layang PQRS adalah 192 cm² ☐ B. Bangun layang-layang memiliki dua pasang sisi yang sama panjang ☐ C. Layang-layang memiliki dua sumbu simetri lipat ☐ D. Salah satu diagonal membagi diagonal yang lain menjadi dua bagian yang sama panjang [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -953,7 +997,11 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -963,27 +1011,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 13: contoh soal numerasi sederhana.</t>
+          <t>Sebuah taman mini berbentuk gabungan persegi panjang berukuran panjang 20 m dan lebar 14 m dengan setengah lingkaran pada salah satu sisi lebarnya (d = 14 m). Berapakah keliling batas luar taman mini tersebut? (Gunakan π = 22/7)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 68 meter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 74 meter</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 76 meter</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 82 meter</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -994,7 +1042,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1056,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 14: contoh soal numerasi sederhana.</t>
+          <t>Sebuah bak penampungan air berbentuk balok memiliki ukuran panjang 2 meter, lebar 1,5 meter, dan tinggi 1 meter. Jika bak tersebut telah terisi air sebanyak 3/4 dari kapasitas tampung penuhnya, berapa liter air yang sudah ada di dalam bak?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 1.850 liter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 2.100 liter</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 2.250 liter</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 2.500 liter</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,17 +1087,21 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 15: contoh soal numerasi sederhana.</t>
+          <t>Sebuah tempat sampah berbentuk kubus terbuka (tanpa tutup bagian atas) dibuat dari plat seng dengan panjang rusuk 50 cm. Tentukan kebenaran dari pernyataan-pernyataan berikut! [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1076,7 +1132,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1146,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 16: contoh soal numerasi sederhana.</t>
+          <t>Hasil panen mangga Arumanis Pak Karyo selama 6 minggu (dalam kg) adalah sebagai berikut: 85, 92, 78, 90, 88, 95. Rata-rata hasil panen mangga Pak Karyo per minggu adalah...</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 86 kg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 88 kg</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 89 kg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 91 kg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1177,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1191,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 17: contoh soal numerasi sederhana.</t>
+          <t>Berikut data nilai tes literasi membaca 11 siswa SD: 65, 70, 75, 75, 80, 80, 80, 85, 90, 90, 95. Modus dan median dari data tersebut adalah...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. Modus = 80 dan Median = 80</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Modus = 80 dan Median = 75</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. Modus = 75 dan Median = 80</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Modus = 80 dan Median = 82,5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,17 +1222,21 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 18: contoh soal numerasi sederhana.</t>
+          <t>Sebuah koperasi siswa mendistribusikan 720 buku bacaan fiksi dengan diagram lingkaran sudut pusat: • Komik Edukasi = 120° • Novel Anak = 90° • Dongeng Nusantara = 100° • Cerita Fabel = sisanya (50°) Manakah pernyataan berikut yang BENAR? (Jawaban benar lebih dari satu) ☐ A. Buku Komik Edukasi yang didistribusikan berjumlah 240 buku ☐ B. Buku Novel Anak berjumlah 180 buku ☐ C. Jumlah buku Cerita Fabel yang memiliki sudut 50° adalah 100 buku ☐ D. Selisih antara buku Komik Edukasi dan Novel Anak adalah 60 buku [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1199,17 +1267,21 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 19: contoh soal numerasi sederhana.</t>
+          <t>Sebuah koperasi siswa mendistribusikan 720 buku bacaan fiksi dengan diagram lingkaran sudut pusat: • Komik Edukasi = 120° • Novel Anak = 90° • Dongeng Nusantara = 100° • Cerita Fabel = sisanya (50°) Manakah pernyataan berikut yang BENAR? (Jawaban benar lebih dari satu) ☐ A. Buku Komik Edukasi yang didistribusikan berjumlah 240 buku ☐ B. Buku Novel Anak berjumlah 180 buku ☐ C. Jumlah buku Cerita Fabel yang tersedia adalah 120 buku ☐ D. Selisih antara buku Komik Edukasi dan Novel Anak adalah 60 buku [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1240,7 +1312,11 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1250,27 +1326,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 10] Soal Matematika 20: contoh soal numerasi sederhana.</t>
+          <t>Titik A(3, 2) dirotasikan sebesar 90° berlawanan arah putaran jarum jam dengan pusat rotasi di titik O(0, 0). Koordinat titik bayangan A' adalah...</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. A'(-2, 3)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. A'(2, -3)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. A'(-3, 2)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. A'(-2, -3)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1281,7 +1357,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
